--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008439271833561955</v>
       </c>
       <c r="C2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>18914924</v>
+        <v>4501781</v>
       </c>
       <c r="L2" t="n">
-        <v>11168943</v>
+        <v>2492050</v>
       </c>
       <c r="M2" t="n">
-        <v>2779427</v>
+        <v>593537</v>
       </c>
       <c r="N2" t="n">
-        <v>93462</v>
+        <v>16087</v>
       </c>
       <c r="O2" t="n">
-        <v>1636861</v>
+        <v>361670</v>
       </c>
       <c r="P2" t="n">
-        <v>564959</v>
+        <v>127481</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9204797148704529</v>
+        <v>0.8732711672782898</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8483067154884338</v>
+        <v>0.7602293491363525</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8077766299247742</v>
+        <v>0.6874558329582214</v>
       </c>
       <c r="U2" t="n">
-        <v>0.31021848320961</v>
+        <v>0.2210906744003296</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8192042112350464</v>
+        <v>0.7265046834945679</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9268049597740173</v>
+        <v>0.854607880115509</v>
       </c>
       <c r="X2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566228985786438</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112591743469238</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858102023601532</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624639630317688</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020282030105591</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002023734838753813</v>
       </c>
       <c r="C3" t="n">
-        <v>1448</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>18914924</v>
+        <v>4501781</v>
       </c>
       <c r="E3" t="n">
-        <v>1196096</v>
+        <v>514313</v>
       </c>
       <c r="F3" t="n">
-        <v>10967</v>
+        <v>6039</v>
       </c>
       <c r="G3" t="n">
-        <v>1148</v>
+        <v>500</v>
       </c>
       <c r="H3" t="n">
-        <v>377</v>
+        <v>231</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>40064948</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>43559372</v>
+        <v>10653074</v>
       </c>
       <c r="L3" t="n">
-        <v>50273433</v>
+        <v>12274739</v>
       </c>
       <c r="M3" t="n">
-        <v>60929114</v>
+        <v>15127164</v>
       </c>
       <c r="N3" t="n">
-        <v>64754195</v>
+        <v>16183734</v>
       </c>
       <c r="O3" t="n">
-        <v>62920836</v>
+        <v>15684070</v>
       </c>
       <c r="P3" t="n">
-        <v>64500590</v>
+        <v>16114566</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9398735165596008</v>
+        <v>0.8961926698684692</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8560053706169128</v>
+        <v>0.7623542547225952</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7455790638923645</v>
+        <v>0.6364386677742004</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2622471451759338</v>
+        <v>0.180365726351738</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8038352727890015</v>
+        <v>0.7100228071212769</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7306839823722839</v>
+        <v>0.6593412756919861</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>791602</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34131</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27146</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40066488</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44319573</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>51114353</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>61061800</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64841808</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63082667</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64492192</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576059579849243</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100238084793091</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576881885528564</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66196209192276</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016556143760681</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1524903</v>
+        <v>616819</v>
       </c>
       <c r="E4" t="n">
-        <v>11168943</v>
+        <v>2492050</v>
       </c>
       <c r="F4" t="n">
-        <v>332544</v>
+        <v>146242</v>
       </c>
       <c r="G4" t="n">
-        <v>7154</v>
+        <v>4251</v>
       </c>
       <c r="H4" t="n">
-        <v>13484</v>
+        <v>9023</v>
       </c>
       <c r="I4" t="n">
-        <v>721</v>
+        <v>502</v>
       </c>
       <c r="J4" t="n">
-        <v>1540</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>1634061</v>
+        <v>653297</v>
       </c>
       <c r="L4" t="n">
-        <v>1997218</v>
+        <v>785974</v>
       </c>
       <c r="M4" t="n">
-        <v>661409</v>
+        <v>269845</v>
       </c>
       <c r="N4" t="n">
-        <v>207816</v>
+        <v>56675</v>
       </c>
       <c r="O4" t="n">
-        <v>361250</v>
+        <v>136152</v>
       </c>
       <c r="P4" t="n">
-        <v>44618</v>
+        <v>21688</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.930075466632843</v>
+        <v>0.8845835328102112</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8521386384963989</v>
+        <v>0.7612903118133545</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7754326462745667</v>
+        <v>0.6609642505645752</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2842228412628174</v>
+        <v>0.1986625641584396</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8114470243453979</v>
+        <v>0.7181691527366638</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8171415328979492</v>
+        <v>0.7443819642066956</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>815845</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>331353</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21937</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>873860</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1156298</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528723</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120203</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199419</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571141600608826</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910641074180603</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578950166702271</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622129082679749</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018418788909912</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>68589</v>
+        <v>22637</v>
       </c>
       <c r="E5" t="n">
-        <v>704141</v>
+        <v>239700</v>
       </c>
       <c r="F5" t="n">
-        <v>2779427</v>
+        <v>593537</v>
       </c>
       <c r="G5" t="n">
-        <v>53227</v>
+        <v>17437</v>
       </c>
       <c r="H5" t="n">
-        <v>117383</v>
+        <v>55947</v>
       </c>
       <c r="I5" t="n">
-        <v>5110</v>
+        <v>3333</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1210043</v>
+        <v>521448</v>
       </c>
       <c r="L5" t="n">
-        <v>1878806</v>
+        <v>776837</v>
       </c>
       <c r="M5" t="n">
-        <v>948450</v>
+        <v>339054</v>
       </c>
       <c r="N5" t="n">
-        <v>262927</v>
+        <v>73104</v>
       </c>
       <c r="O5" t="n">
-        <v>399453</v>
+        <v>147708</v>
       </c>
       <c r="P5" t="n">
-        <v>208233</v>
+        <v>65865</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9564578533172607</v>
+        <v>0.9280604124069214</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9406595230102539</v>
+        <v>0.904295802116394</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9753536581993103</v>
+        <v>0.9627119302749634</v>
       </c>
       <c r="U5" t="n">
-        <v>0.992793083190918</v>
+        <v>0.9920525550842285</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9883539080619812</v>
+        <v>0.9826168417930603</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9961289763450623</v>
+        <v>0.9946383833885193</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32012</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339750</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39755</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116472</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>853179</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1173987</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530521</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120473</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200260</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735596776008606</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643242359161377</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837833642959595</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963153600692749</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938810467720032</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998375415802002</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>40265</v>
+        <v>13742</v>
       </c>
       <c r="E6" t="n">
-        <v>76137</v>
+        <v>18071</v>
       </c>
       <c r="F6" t="n">
-        <v>114151</v>
+        <v>30870</v>
       </c>
       <c r="G6" t="n">
-        <v>93462</v>
+        <v>16087</v>
       </c>
       <c r="H6" t="n">
-        <v>31366</v>
+        <v>9885</v>
       </c>
       <c r="I6" t="n">
-        <v>927</v>
+        <v>515</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25780</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21382</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43482</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27905</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>19876</v>
+        <v>13289</v>
       </c>
       <c r="F7" t="n">
-        <v>198987</v>
+        <v>83907</v>
       </c>
       <c r="G7" t="n">
-        <v>142582</v>
+        <v>33125</v>
       </c>
       <c r="H7" t="n">
-        <v>1636861</v>
+        <v>361670</v>
       </c>
       <c r="I7" t="n">
-        <v>37853</v>
+        <v>17335</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3240</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118437</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30304</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>149</v>
+        <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>968</v>
+        <v>601</v>
       </c>
       <c r="F8" t="n">
-        <v>4760</v>
+        <v>2787</v>
       </c>
       <c r="G8" t="n">
-        <v>3705</v>
+        <v>1362</v>
       </c>
       <c r="H8" t="n">
-        <v>198640</v>
+        <v>61066</v>
       </c>
       <c r="I8" t="n">
-        <v>564959</v>
+        <v>127481</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
